--- a/FII_DII/fii_dii_data.xlsx
+++ b/FII_DII/fii_dii_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -733,6 +733,29 @@
         <v>1666.98</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>46070</v>
+      </c>
+      <c r="B14" t="n">
+        <v>8867.620000000001</v>
+      </c>
+      <c r="C14" t="n">
+        <v>7872.41</v>
+      </c>
+      <c r="D14" t="n">
+        <v>995.21</v>
+      </c>
+      <c r="E14" t="n">
+        <v>12482.64</v>
+      </c>
+      <c r="F14" t="n">
+        <v>12295.6</v>
+      </c>
+      <c r="G14" t="n">
+        <v>187.04</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/FII_DII/fii_dii_data.xlsx
+++ b/FII_DII/fii_dii_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -756,6 +756,52 @@
         <v>187.04</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>46071</v>
+      </c>
+      <c r="B15" t="n">
+        <v>9720.92</v>
+      </c>
+      <c r="C15" t="n">
+        <v>8566.58</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1154.34</v>
+      </c>
+      <c r="E15" t="n">
+        <v>12143.76</v>
+      </c>
+      <c r="F15" t="n">
+        <v>11703.42</v>
+      </c>
+      <c r="G15" t="n">
+        <v>440.34</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>46072</v>
+      </c>
+      <c r="B16" t="n">
+        <v>8614.9</v>
+      </c>
+      <c r="C16" t="n">
+        <v>9495.389999999999</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-880.49</v>
+      </c>
+      <c r="E16" t="n">
+        <v>11483.86</v>
+      </c>
+      <c r="F16" t="n">
+        <v>12080.14</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-596.28</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/FII_DII/fii_dii_data.xlsx
+++ b/FII_DII/fii_dii_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -802,6 +802,29 @@
         <v>-596.28</v>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>46073</v>
+      </c>
+      <c r="B17" t="n">
+        <v>10010.06</v>
+      </c>
+      <c r="C17" t="n">
+        <v>10944.67</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-934.61</v>
+      </c>
+      <c r="E17" t="n">
+        <v>14901.9</v>
+      </c>
+      <c r="F17" t="n">
+        <v>12264.75</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2637.15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/FII_DII/fii_dii_data.xlsx
+++ b/FII_DII/fii_dii_data.xlsx
@@ -20,13 +20,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +48,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -417,48 +429,48 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>FII_Gross_Purchase</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>FII_Gross_Sales</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>FII_Net</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>DII_Gross_Purchase</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>DII_Gross_Sales</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>DII_Net</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>46054</v>
       </c>
       <c r="B2" t="n">
@@ -481,7 +493,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>46055</v>
       </c>
       <c r="B3" t="n">
@@ -504,7 +516,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>46056</v>
       </c>
       <c r="B4" t="n">
@@ -527,7 +539,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>46057</v>
       </c>
       <c r="B5" t="n">
@@ -550,7 +562,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>46058</v>
       </c>
       <c r="B6" t="n">
@@ -573,7 +585,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>46059</v>
       </c>
       <c r="B7" t="n">
@@ -596,7 +608,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>46062</v>
       </c>
       <c r="B8" t="n">
@@ -619,7 +631,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>46063</v>
       </c>
       <c r="B9" t="n">
@@ -642,7 +654,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>46064</v>
       </c>
       <c r="B10" t="n">
@@ -665,7 +677,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>46065</v>
       </c>
       <c r="B11" t="n">
@@ -688,7 +700,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>46066</v>
       </c>
       <c r="B12" t="n">
@@ -711,7 +723,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>46069</v>
       </c>
       <c r="B13" t="n">
@@ -734,7 +746,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>46070</v>
       </c>
       <c r="B14" t="n">
@@ -757,7 +769,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>46071</v>
       </c>
       <c r="B15" t="n">
@@ -780,7 +792,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>46072</v>
       </c>
       <c r="B16" t="n">
@@ -803,7 +815,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>46073</v>
       </c>
       <c r="B17" t="n">
@@ -823,6 +835,121 @@
       </c>
       <c r="G17" t="n">
         <v>2637.15</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="B18" t="n">
+        <v>12737.34</v>
+      </c>
+      <c r="C18" t="n">
+        <v>16032.98</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-3295.64</v>
+      </c>
+      <c r="E18" t="n">
+        <v>21110.66</v>
+      </c>
+      <c r="F18" t="n">
+        <v>12516.79</v>
+      </c>
+      <c r="G18" t="n">
+        <v>8593.870000000001</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B19" t="n">
+        <v>19120.99</v>
+      </c>
+      <c r="C19" t="n">
+        <v>27873.64</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-8752.65</v>
+      </c>
+      <c r="E19" t="n">
+        <v>26259.37</v>
+      </c>
+      <c r="F19" t="n">
+        <v>14191.2</v>
+      </c>
+      <c r="G19" t="n">
+        <v>12068.17</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="B20" t="n">
+        <v>14914.99</v>
+      </c>
+      <c r="C20" t="n">
+        <v>18667.51</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-3752.52</v>
+      </c>
+      <c r="E20" t="n">
+        <v>18821.1</v>
+      </c>
+      <c r="F20" t="n">
+        <v>13667.73</v>
+      </c>
+      <c r="G20" t="n">
+        <v>5153.37</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>46087</v>
+      </c>
+      <c r="B21" t="n">
+        <v>14434.69</v>
+      </c>
+      <c r="C21" t="n">
+        <v>20465.07</v>
+      </c>
+      <c r="D21" t="n">
+        <v>-6030.38</v>
+      </c>
+      <c r="E21" t="n">
+        <v>19662.38</v>
+      </c>
+      <c r="F21" t="n">
+        <v>12690.87</v>
+      </c>
+      <c r="G21" t="n">
+        <v>6971.51</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B22" t="n">
+        <v>11156.99</v>
+      </c>
+      <c r="C22" t="n">
+        <v>17502.56</v>
+      </c>
+      <c r="D22" t="n">
+        <v>-6345.57</v>
+      </c>
+      <c r="E22" t="n">
+        <v>21586.46</v>
+      </c>
+      <c r="F22" t="n">
+        <v>12572.66</v>
+      </c>
+      <c r="G22" t="n">
+        <v>9013.799999999999</v>
       </c>
     </row>
   </sheetData>

--- a/FII_DII/fii_dii_data.xlsx
+++ b/FII_DII/fii_dii_data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -952,6 +952,52 @@
         <v>9013.799999999999</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B23" t="n">
+        <v>13188.32</v>
+      </c>
+      <c r="C23" t="n">
+        <v>17860.96</v>
+      </c>
+      <c r="D23" t="n">
+        <v>-4672.64</v>
+      </c>
+      <c r="E23" t="n">
+        <v>17202.49</v>
+      </c>
+      <c r="F23" t="n">
+        <v>10869.23</v>
+      </c>
+      <c r="G23" t="n">
+        <v>6333.26</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B24" t="n">
+        <v>11448.68</v>
+      </c>
+      <c r="C24" t="n">
+        <v>17715.99</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-6267.31</v>
+      </c>
+      <c r="E24" t="n">
+        <v>16044.16</v>
+      </c>
+      <c r="F24" t="n">
+        <v>11078.63</v>
+      </c>
+      <c r="G24" t="n">
+        <v>4965.53</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/FII_DII/fii_dii_data.xlsx
+++ b/FII_DII/fii_dii_data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -839,163 +839,646 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>46083</v>
+        <v>46076</v>
       </c>
       <c r="B18" t="n">
-        <v>12737.34</v>
+        <v>15294.02</v>
       </c>
       <c r="C18" t="n">
-        <v>16032.98</v>
+        <v>11810.32</v>
       </c>
       <c r="D18" t="n">
-        <v>-3295.64</v>
+        <v>3483.7</v>
       </c>
       <c r="E18" t="n">
-        <v>21110.66</v>
+        <v>12360.86</v>
       </c>
       <c r="F18" t="n">
-        <v>12516.79</v>
+        <v>13653.1</v>
       </c>
       <c r="G18" t="n">
-        <v>8593.870000000001</v>
+        <v>-1292.24</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>46085</v>
+        <v>46077</v>
       </c>
       <c r="B19" t="n">
-        <v>19120.99</v>
+        <v>20550.91</v>
       </c>
       <c r="C19" t="n">
-        <v>27873.64</v>
+        <v>20653.44</v>
       </c>
       <c r="D19" t="n">
-        <v>-8752.65</v>
+        <v>-102.53</v>
       </c>
       <c r="E19" t="n">
-        <v>26259.37</v>
+        <v>18580.96</v>
       </c>
       <c r="F19" t="n">
-        <v>14191.2</v>
+        <v>15419.74</v>
       </c>
       <c r="G19" t="n">
-        <v>12068.17</v>
+        <v>3161.22</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>46086</v>
+        <v>46078</v>
       </c>
       <c r="B20" t="n">
-        <v>14914.99</v>
+        <v>30369.48</v>
       </c>
       <c r="C20" t="n">
-        <v>18667.51</v>
+        <v>27377.84</v>
       </c>
       <c r="D20" t="n">
-        <v>-3752.52</v>
+        <v>2991.64</v>
       </c>
       <c r="E20" t="n">
-        <v>18821.1</v>
+        <v>18346.49</v>
       </c>
       <c r="F20" t="n">
-        <v>13667.73</v>
+        <v>13227.92</v>
       </c>
       <c r="G20" t="n">
-        <v>5153.37</v>
+        <v>5118.57</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>46087</v>
+        <v>46079</v>
       </c>
       <c r="B21" t="n">
-        <v>14434.69</v>
+        <v>14607.9</v>
       </c>
       <c r="C21" t="n">
-        <v>20465.07</v>
+        <v>18073.89</v>
       </c>
       <c r="D21" t="n">
-        <v>-6030.38</v>
+        <v>-3465.99</v>
       </c>
       <c r="E21" t="n">
-        <v>19662.38</v>
+        <v>19242.72</v>
       </c>
       <c r="F21" t="n">
-        <v>12690.87</v>
+        <v>14211.15</v>
       </c>
       <c r="G21" t="n">
-        <v>6971.51</v>
+        <v>5031.57</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>46090</v>
+        <v>46080</v>
       </c>
       <c r="B22" t="n">
-        <v>11156.99</v>
+        <v>36699.66</v>
       </c>
       <c r="C22" t="n">
-        <v>17502.56</v>
+        <v>44236.02</v>
       </c>
       <c r="D22" t="n">
-        <v>-6345.57</v>
+        <v>-7536.36</v>
       </c>
       <c r="E22" t="n">
-        <v>21586.46</v>
+        <v>24867.72</v>
       </c>
       <c r="F22" t="n">
-        <v>12572.66</v>
+        <v>12574.91</v>
       </c>
       <c r="G22" t="n">
-        <v>9013.799999999999</v>
+        <v>12292.81</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>46091</v>
+        <v>46083</v>
       </c>
       <c r="B23" t="n">
-        <v>13188.32</v>
+        <v>12737.34</v>
       </c>
       <c r="C23" t="n">
-        <v>17860.96</v>
+        <v>16032.98</v>
       </c>
       <c r="D23" t="n">
-        <v>-4672.64</v>
+        <v>-3295.64</v>
       </c>
       <c r="E23" t="n">
-        <v>17202.49</v>
+        <v>21110.66</v>
       </c>
       <c r="F23" t="n">
-        <v>10869.23</v>
+        <v>12516.79</v>
       </c>
       <c r="G23" t="n">
-        <v>6333.26</v>
+        <v>8593.870000000001</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B24" t="n">
+        <v>19120.99</v>
+      </c>
+      <c r="C24" t="n">
+        <v>27873.64</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-8752.65</v>
+      </c>
+      <c r="E24" t="n">
+        <v>26259.37</v>
+      </c>
+      <c r="F24" t="n">
+        <v>14191.2</v>
+      </c>
+      <c r="G24" t="n">
+        <v>12068.17</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="B25" t="n">
+        <v>14914.99</v>
+      </c>
+      <c r="C25" t="n">
+        <v>18667.51</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-3752.52</v>
+      </c>
+      <c r="E25" t="n">
+        <v>18821.1</v>
+      </c>
+      <c r="F25" t="n">
+        <v>13667.73</v>
+      </c>
+      <c r="G25" t="n">
+        <v>5153.37</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>46087</v>
+      </c>
+      <c r="B26" t="n">
+        <v>14434.69</v>
+      </c>
+      <c r="C26" t="n">
+        <v>20465.07</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-6030.38</v>
+      </c>
+      <c r="E26" t="n">
+        <v>19662.38</v>
+      </c>
+      <c r="F26" t="n">
+        <v>12690.87</v>
+      </c>
+      <c r="G26" t="n">
+        <v>6971.51</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B27" t="n">
+        <v>11156.99</v>
+      </c>
+      <c r="C27" t="n">
+        <v>17502.56</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-6345.57</v>
+      </c>
+      <c r="E27" t="n">
+        <v>21586.46</v>
+      </c>
+      <c r="F27" t="n">
+        <v>12572.66</v>
+      </c>
+      <c r="G27" t="n">
+        <v>9013.799999999999</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B28" t="n">
+        <v>13188.32</v>
+      </c>
+      <c r="C28" t="n">
+        <v>17860.96</v>
+      </c>
+      <c r="D28" t="n">
+        <v>-4672.64</v>
+      </c>
+      <c r="E28" t="n">
+        <v>17202.49</v>
+      </c>
+      <c r="F28" t="n">
+        <v>10869.23</v>
+      </c>
+      <c r="G28" t="n">
+        <v>6333.26</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
         <v>46092</v>
       </c>
-      <c r="B24" t="n">
+      <c r="B29" t="n">
         <v>11448.68</v>
       </c>
-      <c r="C24" t="n">
+      <c r="C29" t="n">
         <v>17715.99</v>
       </c>
-      <c r="D24" t="n">
+      <c r="D29" t="n">
         <v>-6267.31</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E29" t="n">
         <v>16044.16</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F29" t="n">
         <v>11078.63</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G29" t="n">
         <v>4965.53</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B30" t="n">
+        <v>15373.05</v>
+      </c>
+      <c r="C30" t="n">
+        <v>22422.92</v>
+      </c>
+      <c r="D30" t="n">
+        <v>-7049.87</v>
+      </c>
+      <c r="E30" t="n">
+        <v>19439.56</v>
+      </c>
+      <c r="F30" t="n">
+        <v>11989.79</v>
+      </c>
+      <c r="G30" t="n">
+        <v>7449.77</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B31" t="n">
+        <v>11923.16</v>
+      </c>
+      <c r="C31" t="n">
+        <v>22639.8</v>
+      </c>
+      <c r="D31" t="n">
+        <v>-10716.64</v>
+      </c>
+      <c r="E31" t="n">
+        <v>22707.84</v>
+      </c>
+      <c r="F31" t="n">
+        <v>12730.42</v>
+      </c>
+      <c r="G31" t="n">
+        <v>9977.42</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B32" t="n">
+        <v>11566.51</v>
+      </c>
+      <c r="C32" t="n">
+        <v>20932.03</v>
+      </c>
+      <c r="D32" t="n">
+        <v>-9365.52</v>
+      </c>
+      <c r="E32" t="n">
+        <v>25150.41</v>
+      </c>
+      <c r="F32" t="n">
+        <v>12557.05</v>
+      </c>
+      <c r="G32" t="n">
+        <v>12593.36</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B33" t="n">
+        <v>11903.71</v>
+      </c>
+      <c r="C33" t="n">
+        <v>16644.93</v>
+      </c>
+      <c r="D33" t="n">
+        <v>-4741.22</v>
+      </c>
+      <c r="E33" t="n">
+        <v>16762.65</v>
+      </c>
+      <c r="F33" t="n">
+        <v>11537.33</v>
+      </c>
+      <c r="G33" t="n">
+        <v>5225.32</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B34" t="n">
+        <v>12798.8</v>
+      </c>
+      <c r="C34" t="n">
+        <v>15513.15</v>
+      </c>
+      <c r="D34" t="n">
+        <v>-2714.35</v>
+      </c>
+      <c r="E34" t="n">
+        <v>16105.2</v>
+      </c>
+      <c r="F34" t="n">
+        <v>12852.17</v>
+      </c>
+      <c r="G34" t="n">
+        <v>3253.03</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B35" t="n">
+        <v>10012.07</v>
+      </c>
+      <c r="C35" t="n">
+        <v>17570.26</v>
+      </c>
+      <c r="D35" t="n">
+        <v>-7558.19</v>
+      </c>
+      <c r="E35" t="n">
+        <v>16926.98</v>
+      </c>
+      <c r="F35" t="n">
+        <v>13063.02</v>
+      </c>
+      <c r="G35" t="n">
+        <v>3863.96</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B36" t="n">
+        <v>28496.17</v>
+      </c>
+      <c r="C36" t="n">
+        <v>34014.56</v>
+      </c>
+      <c r="D36" t="n">
+        <v>-5518.39</v>
+      </c>
+      <c r="E36" t="n">
+        <v>22938.31</v>
+      </c>
+      <c r="F36" t="n">
+        <v>17232.08</v>
+      </c>
+      <c r="G36" t="n">
+        <v>5706.23</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>46104</v>
+      </c>
+      <c r="B37" t="n">
+        <v>10330.98</v>
+      </c>
+      <c r="C37" t="n">
+        <v>20745.21</v>
+      </c>
+      <c r="D37" t="n">
+        <v>-10414.23</v>
+      </c>
+      <c r="E37" t="n">
+        <v>25952.98</v>
+      </c>
+      <c r="F37" t="n">
+        <v>13919.01</v>
+      </c>
+      <c r="G37" t="n">
+        <v>12033.97</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>46105</v>
+      </c>
+      <c r="B38" t="n">
+        <v>12406.9</v>
+      </c>
+      <c r="C38" t="n">
+        <v>20416.46</v>
+      </c>
+      <c r="D38" t="n">
+        <v>-8009.56</v>
+      </c>
+      <c r="E38" t="n">
+        <v>21126.99</v>
+      </c>
+      <c r="F38" t="n">
+        <v>15259.84</v>
+      </c>
+      <c r="G38" t="n">
+        <v>5867.15</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>46106</v>
+      </c>
+      <c r="B39" t="n">
+        <v>14547.7</v>
+      </c>
+      <c r="C39" t="n">
+        <v>16353.07</v>
+      </c>
+      <c r="D39" t="n">
+        <v>-1805.37</v>
+      </c>
+      <c r="E39" t="n">
+        <v>22921.89</v>
+      </c>
+      <c r="F39" t="n">
+        <v>17492.11</v>
+      </c>
+      <c r="G39" t="n">
+        <v>5429.78</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="B40" t="n">
+        <v>20486.39</v>
+      </c>
+      <c r="C40" t="n">
+        <v>24853.69</v>
+      </c>
+      <c r="D40" t="n">
+        <v>-4367.3</v>
+      </c>
+      <c r="E40" t="n">
+        <v>37579.14</v>
+      </c>
+      <c r="F40" t="n">
+        <v>34012.99</v>
+      </c>
+      <c r="G40" t="n">
+        <v>3566.15</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>46111</v>
+      </c>
+      <c r="B41" t="n">
+        <v>21952.95</v>
+      </c>
+      <c r="C41" t="n">
+        <v>33116.01</v>
+      </c>
+      <c r="D41" t="n">
+        <v>-11163.06</v>
+      </c>
+      <c r="E41" t="n">
+        <v>26358.5</v>
+      </c>
+      <c r="F41" t="n">
+        <v>11463.78</v>
+      </c>
+      <c r="G41" t="n">
+        <v>14894.72</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B42" t="n">
+        <v>17958.07</v>
+      </c>
+      <c r="C42" t="n">
+        <v>26289.22</v>
+      </c>
+      <c r="D42" t="n">
+        <v>-8331.15</v>
+      </c>
+      <c r="E42" t="n">
+        <v>18536.73</v>
+      </c>
+      <c r="F42" t="n">
+        <v>11364.93</v>
+      </c>
+      <c r="G42" t="n">
+        <v>7171.8</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>46114</v>
+      </c>
+      <c r="B43" t="n">
+        <v>10626.52</v>
+      </c>
+      <c r="C43" t="n">
+        <v>20557.65</v>
+      </c>
+      <c r="D43" t="n">
+        <v>-9931.129999999999</v>
+      </c>
+      <c r="E43" t="n">
+        <v>18421.27</v>
+      </c>
+      <c r="F43" t="n">
+        <v>11212.86</v>
+      </c>
+      <c r="G43" t="n">
+        <v>7208.41</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="B44" t="n">
+        <v>8837.639999999999</v>
+      </c>
+      <c r="C44" t="n">
+        <v>17004.81</v>
+      </c>
+      <c r="D44" t="n">
+        <v>-8167.17</v>
+      </c>
+      <c r="E44" t="n">
+        <v>20445.57</v>
+      </c>
+      <c r="F44" t="n">
+        <v>12356.87</v>
+      </c>
+      <c r="G44" t="n">
+        <v>8088.7</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>46119</v>
+      </c>
+      <c r="B45" t="n">
+        <v>7953.46</v>
+      </c>
+      <c r="C45" t="n">
+        <v>16645.57</v>
+      </c>
+      <c r="D45" t="n">
+        <v>-8692.110000000001</v>
+      </c>
+      <c r="E45" t="n">
+        <v>20860.09</v>
+      </c>
+      <c r="F45" t="n">
+        <v>12880.59</v>
+      </c>
+      <c r="G45" t="n">
+        <v>7979.5</v>
       </c>
     </row>
   </sheetData>

--- a/FII_DII/fii_dii_data.xlsx
+++ b/FII_DII/fii_dii_data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1481,6 +1481,512 @@
         <v>7979.5</v>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>46120</v>
+      </c>
+      <c r="B46" t="n">
+        <v>19092.05</v>
+      </c>
+      <c r="C46" t="n">
+        <v>21904.02</v>
+      </c>
+      <c r="D46" t="n">
+        <v>-2811.97</v>
+      </c>
+      <c r="E46" t="n">
+        <v>29003.39</v>
+      </c>
+      <c r="F46" t="n">
+        <v>24835.22</v>
+      </c>
+      <c r="G46" t="n">
+        <v>4168.17</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>46121</v>
+      </c>
+      <c r="B47" t="n">
+        <v>15746.32</v>
+      </c>
+      <c r="C47" t="n">
+        <v>17457.51</v>
+      </c>
+      <c r="D47" t="n">
+        <v>-1711.19</v>
+      </c>
+      <c r="E47" t="n">
+        <v>15968.21</v>
+      </c>
+      <c r="F47" t="n">
+        <v>15012.31</v>
+      </c>
+      <c r="G47" t="n">
+        <v>955.9</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>46122</v>
+      </c>
+      <c r="B48" t="n">
+        <v>18303.96</v>
+      </c>
+      <c r="C48" t="n">
+        <v>17631.87</v>
+      </c>
+      <c r="D48" t="n">
+        <v>672.09</v>
+      </c>
+      <c r="E48" t="n">
+        <v>15982.46</v>
+      </c>
+      <c r="F48" t="n">
+        <v>15572.41</v>
+      </c>
+      <c r="G48" t="n">
+        <v>410.05</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>46125</v>
+      </c>
+      <c r="B49" t="n">
+        <v>15382.09</v>
+      </c>
+      <c r="C49" t="n">
+        <v>17365.27</v>
+      </c>
+      <c r="D49" t="n">
+        <v>-1983.18</v>
+      </c>
+      <c r="E49" t="n">
+        <v>16612.03</v>
+      </c>
+      <c r="F49" t="n">
+        <v>14179.73</v>
+      </c>
+      <c r="G49" t="n">
+        <v>2432.3</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>46127</v>
+      </c>
+      <c r="B50" t="n">
+        <v>18075.63</v>
+      </c>
+      <c r="C50" t="n">
+        <v>17409.48</v>
+      </c>
+      <c r="D50" t="n">
+        <v>666.15</v>
+      </c>
+      <c r="E50" t="n">
+        <v>18499.57</v>
+      </c>
+      <c r="F50" t="n">
+        <v>19068.55</v>
+      </c>
+      <c r="G50" t="n">
+        <v>-568.98</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>46128</v>
+      </c>
+      <c r="B51" t="n">
+        <v>16209.44</v>
+      </c>
+      <c r="C51" t="n">
+        <v>15827.08</v>
+      </c>
+      <c r="D51" t="n">
+        <v>382.36</v>
+      </c>
+      <c r="E51" t="n">
+        <v>16538.08</v>
+      </c>
+      <c r="F51" t="n">
+        <v>19965.83</v>
+      </c>
+      <c r="G51" t="n">
+        <v>-3427.75</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>46129</v>
+      </c>
+      <c r="B52" t="n">
+        <v>16034.88</v>
+      </c>
+      <c r="C52" t="n">
+        <v>15351.68</v>
+      </c>
+      <c r="D52" t="n">
+        <v>683.2</v>
+      </c>
+      <c r="E52" t="n">
+        <v>17513.99</v>
+      </c>
+      <c r="F52" t="n">
+        <v>22235.47</v>
+      </c>
+      <c r="G52" t="n">
+        <v>-4721.48</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>46132</v>
+      </c>
+      <c r="B53" t="n">
+        <v>12756.88</v>
+      </c>
+      <c r="C53" t="n">
+        <v>13816.81</v>
+      </c>
+      <c r="D53" t="n">
+        <v>-1059.93</v>
+      </c>
+      <c r="E53" t="n">
+        <v>18753.06</v>
+      </c>
+      <c r="F53" t="n">
+        <v>15786.17</v>
+      </c>
+      <c r="G53" t="n">
+        <v>2966.89</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>46133</v>
+      </c>
+      <c r="B54" t="n">
+        <v>13033.17</v>
+      </c>
+      <c r="C54" t="n">
+        <v>14952.16</v>
+      </c>
+      <c r="D54" t="n">
+        <v>-1918.99</v>
+      </c>
+      <c r="E54" t="n">
+        <v>18366.67</v>
+      </c>
+      <c r="F54" t="n">
+        <v>16145.4</v>
+      </c>
+      <c r="G54" t="n">
+        <v>2221.27</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>46134</v>
+      </c>
+      <c r="B55" t="n">
+        <v>13895.07</v>
+      </c>
+      <c r="C55" t="n">
+        <v>15973.43</v>
+      </c>
+      <c r="D55" t="n">
+        <v>-2078.36</v>
+      </c>
+      <c r="E55" t="n">
+        <v>18704.25</v>
+      </c>
+      <c r="F55" t="n">
+        <v>19752.42</v>
+      </c>
+      <c r="G55" t="n">
+        <v>-1048.17</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B56" t="n">
+        <v>12829.12</v>
+      </c>
+      <c r="C56" t="n">
+        <v>16083.83</v>
+      </c>
+      <c r="D56" t="n">
+        <v>-3254.71</v>
+      </c>
+      <c r="E56" t="n">
+        <v>18498.19</v>
+      </c>
+      <c r="F56" t="n">
+        <v>17556.84</v>
+      </c>
+      <c r="G56" t="n">
+        <v>941.35</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>46136</v>
+      </c>
+      <c r="B57" t="n">
+        <v>9837.200000000001</v>
+      </c>
+      <c r="C57" t="n">
+        <v>18665.07</v>
+      </c>
+      <c r="D57" t="n">
+        <v>-8827.870000000001</v>
+      </c>
+      <c r="E57" t="n">
+        <v>21560.16</v>
+      </c>
+      <c r="F57" t="n">
+        <v>16859.45</v>
+      </c>
+      <c r="G57" t="n">
+        <v>4700.71</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B58" t="n">
+        <v>30263.32</v>
+      </c>
+      <c r="C58" t="n">
+        <v>31414.8</v>
+      </c>
+      <c r="D58" t="n">
+        <v>-1151.48</v>
+      </c>
+      <c r="E58" t="n">
+        <v>19978.34</v>
+      </c>
+      <c r="F58" t="n">
+        <v>15854.42</v>
+      </c>
+      <c r="G58" t="n">
+        <v>4123.92</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B59" t="n">
+        <v>17231.5</v>
+      </c>
+      <c r="C59" t="n">
+        <v>19335.24</v>
+      </c>
+      <c r="D59" t="n">
+        <v>-2103.74</v>
+      </c>
+      <c r="E59" t="n">
+        <v>18044.05</v>
+      </c>
+      <c r="F59" t="n">
+        <v>16332.04</v>
+      </c>
+      <c r="G59" t="n">
+        <v>1712.01</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B60" t="n">
+        <v>14271.22</v>
+      </c>
+      <c r="C60" t="n">
+        <v>16739.64</v>
+      </c>
+      <c r="D60" t="n">
+        <v>-2468.42</v>
+      </c>
+      <c r="E60" t="n">
+        <v>17232.28</v>
+      </c>
+      <c r="F60" t="n">
+        <v>14970.11</v>
+      </c>
+      <c r="G60" t="n">
+        <v>2262.17</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B61" t="n">
+        <v>15049.55</v>
+      </c>
+      <c r="C61" t="n">
+        <v>23097.41</v>
+      </c>
+      <c r="D61" t="n">
+        <v>-8047.86</v>
+      </c>
+      <c r="E61" t="n">
+        <v>18252.89</v>
+      </c>
+      <c r="F61" t="n">
+        <v>14765.79</v>
+      </c>
+      <c r="G61" t="n">
+        <v>3487.1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B62" t="n">
+        <v>19660.47</v>
+      </c>
+      <c r="C62" t="n">
+        <v>16824.85</v>
+      </c>
+      <c r="D62" t="n">
+        <v>2835.62</v>
+      </c>
+      <c r="E62" t="n">
+        <v>19516.11</v>
+      </c>
+      <c r="F62" t="n">
+        <v>14751.95</v>
+      </c>
+      <c r="G62" t="n">
+        <v>4764.16</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B63" t="n">
+        <v>10392.91</v>
+      </c>
+      <c r="C63" t="n">
+        <v>14014.49</v>
+      </c>
+      <c r="D63" t="n">
+        <v>-3621.58</v>
+      </c>
+      <c r="E63" t="n">
+        <v>16234.31</v>
+      </c>
+      <c r="F63" t="n">
+        <v>13631.69</v>
+      </c>
+      <c r="G63" t="n">
+        <v>2602.62</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B64" t="n">
+        <v>14459.21</v>
+      </c>
+      <c r="C64" t="n">
+        <v>20294.11</v>
+      </c>
+      <c r="D64" t="n">
+        <v>-5834.9</v>
+      </c>
+      <c r="E64" t="n">
+        <v>22888.16</v>
+      </c>
+      <c r="F64" t="n">
+        <v>16051.29</v>
+      </c>
+      <c r="G64" t="n">
+        <v>6836.87</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B65" t="n">
+        <v>17997.95</v>
+      </c>
+      <c r="C65" t="n">
+        <v>18338.84</v>
+      </c>
+      <c r="D65" t="n">
+        <v>-340.89</v>
+      </c>
+      <c r="E65" t="n">
+        <v>17032.05</v>
+      </c>
+      <c r="F65" t="n">
+        <v>16590.98</v>
+      </c>
+      <c r="G65" t="n">
+        <v>441.07</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B66" t="n">
+        <v>15083.49</v>
+      </c>
+      <c r="C66" t="n">
+        <v>19194.09</v>
+      </c>
+      <c r="D66" t="n">
+        <v>-4110.6</v>
+      </c>
+      <c r="E66" t="n">
+        <v>21296.87</v>
+      </c>
+      <c r="F66" t="n">
+        <v>14548.74</v>
+      </c>
+      <c r="G66" t="n">
+        <v>6748.13</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="B67" t="n">
+        <v>12813.74</v>
+      </c>
+      <c r="C67" t="n">
+        <v>21251.3</v>
+      </c>
+      <c r="D67" t="n">
+        <v>-8437.559999999999</v>
+      </c>
+      <c r="E67" t="n">
+        <v>21626.43</v>
+      </c>
+      <c r="F67" t="n">
+        <v>15686.78</v>
+      </c>
+      <c r="G67" t="n">
+        <v>5939.65</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
